--- a/artfynd/A 21007-2025 artfynd.xlsx
+++ b/artfynd/A 21007-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81678542</v>
+        <v>81678806</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
+        <v>95511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636227.9316746395</v>
+        <v>636195.9644977782</v>
       </c>
       <c r="R2" t="n">
-        <v>6715187.087535432</v>
+        <v>6715445.851361719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>noterad</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96940386</v>
+        <v>81678542</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
+        <v>98431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,26 +825,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Östanå ledningsgata, Upl</t>
+          <t>skog N om Östanå KLG, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636230.8754012659</v>
+        <v>636227.9316746395</v>
       </c>
       <c r="R3" t="n">
-        <v>6715096.105868871</v>
+        <v>6715187.087535432</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -892,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>inom 30m</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +891,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96940298</v>
+        <v>96940386</v>
       </c>
       <c r="B4" t="n">
         <v>101680</v>
@@ -954,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636196.4576289693</v>
+        <v>636230.8754012659</v>
       </c>
       <c r="R4" t="n">
-        <v>6715471.964562267</v>
+        <v>6715096.105868871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,6 +1007,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>inom 30m</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1037,6 +1033,248 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96940632</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95511</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr om Östanå ledningsgata, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>636252.0274699864</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6715267.271444519</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96940298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101680</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr om Östanå ledningsgata, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>636196.4576289693</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6715471.964562267</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
